--- a/3_output/2026/w37/y2026_w37_weekly_report_output.xlsx
+++ b/3_output/2026/w37/y2026_w37_weekly_report_output.xlsx
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="26" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="E26" s="16" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="K26" s="16" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="26" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="E27" s="16" t="n">
         <v>0.08</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>0.02</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="16" t="n">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="26" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E29" s="16" t="n">
         <v>0.06</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="K29" s="16" t="n">
         <v>0.01</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="E30" s="16" t="n">
         <v>0.05</v>
@@ -3412,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="26" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="E31" s="16" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>0.09</v>
       </c>
       <c r="J31" s="26" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="K31" s="16" t="n">
         <v>0.05</v>
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="14" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="K92" s="14" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="E93" s="14" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="K93" s="14" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="E94" s="14" t="n">
         <v>1.3</v>
@@ -6827,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="K94" s="14" t="n">
         <v>0.8</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>6.34</v>
+        <v>6.26</v>
       </c>
       <c r="E95" s="14" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="14" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="K95" s="14" t="n">
         <v>0</v>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>10.46</v>
+        <v>12.38</v>
       </c>
       <c r="E96" s="14" t="n">
         <v>1.1</v>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>10.34</v>
+        <v>7.18</v>
       </c>
       <c r="K96" s="14" t="n">
         <v>0.6</v>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="E97" s="14" t="n">
         <v>1.1</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="14" t="n">
-        <v>12.12</v>
+        <v>12.2</v>
       </c>
       <c r="K97" s="14" t="n">
         <v>1.1</v>
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="14" t="n">
-        <v>12.74</v>
+        <v>12.62</v>
       </c>
       <c r="E98" s="14" t="n">
         <v>0</v>
@@ -7079,7 +7079,7 @@
         <v>6.7</v>
       </c>
       <c r="J98" s="14" t="n">
-        <v>17.48</v>
+        <v>18.12</v>
       </c>
       <c r="K98" s="14" t="n">
         <v>2.8</v>
@@ -7124,7 +7124,7 @@
         <v>19.4</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>5.02</v>
+        <v>6.46</v>
       </c>
       <c r="E99" s="14" t="n">
         <v>1.8</v>
@@ -7142,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>15</v>
+        <v>12.1</v>
       </c>
       <c r="K99" s="14" t="n">
         <v>5.8</v>
@@ -7187,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="14" t="n">
-        <v>17.08</v>
+        <v>16.9</v>
       </c>
       <c r="E100" s="14" t="n">
         <v>0</v>
@@ -7205,7 +7205,7 @@
         <v>16.7</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>8.16</v>
+        <v>8.44</v>
       </c>
       <c r="K100" s="14" t="n">
         <v>3.4</v>
@@ -7250,7 +7250,7 @@
         <v>6.3</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>6.7</v>
+        <v>6.84</v>
       </c>
       <c r="E101" s="14" t="n">
         <v>7.8</v>
@@ -44213,7 +44213,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -44231,7 +44231,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -44257,7 +44257,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="D9" t="n">
         <v>0.08</v>
@@ -44275,7 +44275,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
         <v>0.02</v>
@@ -44301,7 +44301,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -44345,7 +44345,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
@@ -44363,7 +44363,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J11" t="n">
         <v>0.01</v>
@@ -44389,7 +44389,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
@@ -44433,7 +44433,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -44451,7 +44451,7 @@
         <v>0.09</v>
       </c>
       <c r="I13" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="n">
         <v>0.05</v>
@@ -46255,7 +46255,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -46281,7 +46281,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -46299,7 +46299,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -46325,7 +46325,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="D9" t="n">
         <v>1.3</v>
@@ -46343,7 +46343,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="J9" t="n">
         <v>0.8</v>
@@ -46369,7 +46369,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>6.34</v>
+        <v>6.26</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -46387,7 +46387,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -46413,7 +46413,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>10.46</v>
+        <v>12.38</v>
       </c>
       <c r="D11" t="n">
         <v>1.1</v>
@@ -46431,7 +46431,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>10.34</v>
+        <v>7.18</v>
       </c>
       <c r="J11" t="n">
         <v>0.6</v>
@@ -46457,7 +46457,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="D12" t="n">
         <v>1.1</v>
@@ -46475,7 +46475,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>12.12</v>
+        <v>12.2</v>
       </c>
       <c r="J12" t="n">
         <v>1.1</v>
@@ -46501,7 +46501,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74</v>
+        <v>12.62</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -46519,7 +46519,7 @@
         <v>6.7</v>
       </c>
       <c r="I13" t="n">
-        <v>17.48</v>
+        <v>18.12</v>
       </c>
       <c r="J13" t="n">
         <v>2.8</v>
@@ -46545,7 +46545,7 @@
         <v>19.4</v>
       </c>
       <c r="C14" t="n">
-        <v>5.02</v>
+        <v>6.46</v>
       </c>
       <c r="D14" t="n">
         <v>1.8</v>
@@ -46563,7 +46563,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>12.1</v>
       </c>
       <c r="J14" t="n">
         <v>5.8</v>
@@ -46589,7 +46589,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>17.08</v>
+        <v>16.9</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -46607,7 +46607,7 @@
         <v>16.7</v>
       </c>
       <c r="I15" t="n">
-        <v>8.16</v>
+        <v>8.44</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -46633,7 +46633,7 @@
         <v>6.3</v>
       </c>
       <c r="C16" t="n">
-        <v>6.7</v>
+        <v>6.84</v>
       </c>
       <c r="D16" t="n">
         <v>7.8</v>

--- a/3_output/2026/w37/y2026_w37_weekly_report_output.xlsx
+++ b/3_output/2026/w37/y2026_w37_weekly_report_output.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
   <si>
     <t>GRAPH 1A: Vector index for the current week</t>
   </si>
@@ -608,6 +608,96 @@
       </rPr>
       <t>1</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1</t>
   </si>
   <si>
     <t xml:space="preserve">Week: 37</t>
@@ -1998,7 +2088,7 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -2382,27 +2472,17 @@
       <c r="B13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -2433,27 +2513,17 @@
       <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
       <c r="E14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -2485,10 +2555,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>7.087</v>
+        <v>32.6</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.8261</v>
+        <v>3.8</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>0</v>
@@ -2745,11 +2815,11 @@
       <c r="L20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14" t="n">
-        <v>0</v>
+      <c r="M20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2808,11 +2878,11 @@
       <c r="L21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="14" t="n">
-        <v>0</v>
+      <c r="M21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2871,11 +2941,11 @@
       <c r="L22" s="26" t="n">
         <v>0.01</v>
       </c>
-      <c r="M22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="26" t="n">
-        <v>0</v>
+      <c r="M22" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2934,11 +3004,11 @@
       <c r="L23" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="M23" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="26" t="n">
-        <v>0</v>
+      <c r="M23" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2997,11 +3067,11 @@
       <c r="L24" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="M24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>0</v>
+      <c r="M24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -3060,14 +3130,14 @@
       <c r="L25" s="26" t="n">
         <v>0.17</v>
       </c>
-      <c r="M25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="16" t="n">
-        <v>0</v>
+      <c r="M25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -3123,11 +3193,11 @@
       <c r="L26" s="26" t="n">
         <v>0.36</v>
       </c>
-      <c r="M26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="16" t="n">
-        <v>0</v>
+      <c r="M26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -3186,11 +3256,11 @@
       <c r="L27" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="M27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="16" t="n">
-        <v>0</v>
+      <c r="M27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -3249,11 +3319,11 @@
       <c r="L28" s="26" t="n">
         <v>0.32</v>
       </c>
-      <c r="M28" s="16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>0</v>
+      <c r="M28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -3312,11 +3382,11 @@
       <c r="L29" s="26" t="n">
         <v>0.31</v>
       </c>
-      <c r="M29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>0</v>
+      <c r="M29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -3375,11 +3445,11 @@
       <c r="L30" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="M30" s="16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>0.35</v>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -3438,11 +3508,11 @@
       <c r="L31" s="26" t="n">
         <v>0.33</v>
       </c>
-      <c r="M31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="16" t="n">
-        <v>0</v>
+      <c r="M31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -3501,11 +3571,11 @@
       <c r="L32" s="26" t="n">
         <v>0.17</v>
       </c>
-      <c r="M32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="16" t="n">
-        <v>0</v>
+      <c r="M32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3564,11 +3634,11 @@
       <c r="L33" s="26" t="n">
         <v>0.11</v>
       </c>
-      <c r="M33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="16" t="n">
-        <v>0</v>
+      <c r="M33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3601,13 +3671,13 @@
         <v>0.06</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E34" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="F34" s="26" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="G34" s="16" t="n">
         <v>0.04</v>
@@ -3625,13 +3695,13 @@
         <v>0.08</v>
       </c>
       <c r="L34" s="26" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="16" t="n">
-        <v>0</v>
+        <v>0.07</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3804,7 +3874,7 @@
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="5" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -4182,27 +4252,15 @@
       <c r="B47" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
       <c r="F47" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
       <c r="J47" s="12"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -4233,27 +4291,15 @@
       <c r="B48" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
       <c r="F48" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
       <c r="J48" s="12"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -4294,16 +4340,16 @@
         <v>182</v>
       </c>
       <c r="F49" s="33" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G49" s="33" t="n">
-        <v>7.09</v>
+        <v>32.6</v>
       </c>
       <c r="H49" s="33" t="n">
-        <v>0.83</v>
+        <v>3.8</v>
       </c>
       <c r="I49" s="33" t="n">
-        <v>7.91</v>
+        <v>36.4</v>
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="1"/>
@@ -4523,40 +4569,40 @@
         <v>1.22</v>
       </c>
       <c r="D54" s="31" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="E54" s="31" t="n">
         <v>2.3</v>
       </c>
       <c r="F54" s="31" t="n">
-        <v>3.22</v>
+        <v>4.03</v>
       </c>
       <c r="G54" s="31" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="31" t="n">
-        <v>2.85</v>
+        <v>3.56</v>
       </c>
       <c r="I54" s="31" t="n">
         <v>0.89</v>
       </c>
       <c r="J54" s="31" t="n">
-        <v>2.58</v>
+        <v>3.22</v>
       </c>
       <c r="K54" s="31" t="n">
         <v>1.33</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M54" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N54" s="31" t="n">
-        <v>2.4</v>
+        <v>3.46</v>
+      </c>
+      <c r="M54" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="O54" s="33" t="n">
-        <v>5.04</v>
+        <v>23.2</v>
       </c>
       <c r="P54" s="1"/>
       <c r="Q54" s="12"/>
@@ -4586,40 +4632,40 @@
         <v>1.44</v>
       </c>
       <c r="D55" s="31" t="n">
-        <v>3.22</v>
+        <v>4.03</v>
       </c>
       <c r="E55" s="31" t="n">
         <v>4.8</v>
       </c>
       <c r="F55" s="31" t="n">
-        <v>4.14</v>
+        <v>5.18</v>
       </c>
       <c r="G55" s="31" t="n">
         <v>1.8</v>
       </c>
       <c r="H55" s="31" t="n">
-        <v>5.07</v>
+        <v>6.33</v>
       </c>
       <c r="I55" s="31" t="n">
         <v>2</v>
       </c>
       <c r="J55" s="31" t="n">
-        <v>2.89</v>
+        <v>3.61</v>
       </c>
       <c r="K55" s="31" t="n">
         <v>2.47</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="M55" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="N55" s="32" t="n">
-        <v>0.8</v>
+        <v>5.01</v>
+      </c>
+      <c r="M55" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="N55" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="O55" s="33" t="n">
-        <v>4.48</v>
+        <v>20.6</v>
       </c>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
@@ -4675,14 +4721,14 @@
       <c r="L56" s="31" t="n">
         <v>14.24</v>
       </c>
-      <c r="M56" s="32" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="N56" s="32" t="n">
-        <v>5.4</v>
+      <c r="M56" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N56" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="O56" s="33" t="n">
-        <v>6.39</v>
+        <v>29.4</v>
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="12"/>
@@ -4738,14 +4784,14 @@
       <c r="L57" s="31" t="n">
         <v>46.27</v>
       </c>
-      <c r="M57" s="32" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="N57" s="32" t="n">
-        <v>23.7</v>
+      <c r="M57" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="N57" s="32" t="s">
+        <v>68</v>
       </c>
       <c r="O57" s="33" t="n">
-        <v>23.65</v>
+        <v>108.8</v>
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="12"/>
@@ -4801,14 +4847,14 @@
       <c r="L58" s="31" t="n">
         <v>73.21</v>
       </c>
-      <c r="M58" s="33" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="N58" s="33" t="n">
-        <v>13.9</v>
+      <c r="M58" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="N58" s="33" t="s">
+        <v>70</v>
       </c>
       <c r="O58" s="33" t="n">
-        <v>21.87</v>
+        <v>100.6</v>
       </c>
       <c r="P58" s="1"/>
       <c r="Q58" s="12"/>
@@ -4864,14 +4910,14 @@
       <c r="L59" s="31" t="n">
         <v>115.14</v>
       </c>
-      <c r="M59" s="33" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="N59" s="33" t="n">
-        <v>27.4</v>
+      <c r="M59" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="N59" s="33" t="s">
+        <v>72</v>
       </c>
       <c r="O59" s="33" t="n">
-        <v>23.57</v>
+        <v>108.4</v>
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="12"/>
@@ -4927,14 +4973,14 @@
       <c r="L60" s="31" t="n">
         <v>135.15</v>
       </c>
-      <c r="M60" s="33" t="n">
-        <v>21</v>
-      </c>
-      <c r="N60" s="33" t="n">
-        <v>27.4</v>
+      <c r="M60" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="N60" s="33" t="s">
+        <v>72</v>
       </c>
       <c r="O60" s="33" t="n">
-        <v>24.13</v>
+        <v>111</v>
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="12"/>
@@ -4990,14 +5036,14 @@
       <c r="L61" s="31" t="n">
         <v>79.9</v>
       </c>
-      <c r="M61" s="33" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="N61" s="33" t="n">
-        <v>10.6</v>
+      <c r="M61" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="N61" s="33" t="s">
+        <v>75</v>
       </c>
       <c r="O61" s="33" t="n">
-        <v>24.83</v>
+        <v>114.2</v>
       </c>
       <c r="P61" s="1"/>
       <c r="Q61" s="12"/>
@@ -5053,14 +5099,14 @@
       <c r="L62" s="31" t="n">
         <v>54.45</v>
       </c>
-      <c r="M62" s="33" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="N62" s="33" t="n">
-        <v>12.6</v>
+      <c r="M62" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="N62" s="33" t="s">
+        <v>77</v>
       </c>
       <c r="O62" s="33" t="n">
-        <v>19.17</v>
+        <v>88.2</v>
       </c>
       <c r="P62" s="1"/>
       <c r="Q62" s="12"/>
@@ -5116,14 +5162,14 @@
       <c r="L63" s="31" t="n">
         <v>47.21</v>
       </c>
-      <c r="M63" s="33" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="N63" s="33" t="n">
-        <v>28.4</v>
+      <c r="M63" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="N63" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="O63" s="33" t="n">
-        <v>16.7</v>
+        <v>76.8</v>
       </c>
       <c r="P63" s="1"/>
       <c r="Q63" s="12"/>
@@ -5179,14 +5225,14 @@
       <c r="L64" s="31" t="n">
         <v>34.73</v>
       </c>
-      <c r="M64" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="N64" s="33" t="n">
-        <v>124.44</v>
+      <c r="M64" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="N64" s="33" t="s">
+        <v>81</v>
       </c>
       <c r="O64" s="33" t="n">
-        <v>9.83</v>
+        <v>45.2</v>
       </c>
       <c r="P64" s="1"/>
       <c r="Q64" s="12"/>
@@ -5242,14 +5288,14 @@
       <c r="L65" s="31" t="n">
         <v>37.56</v>
       </c>
-      <c r="M65" s="33" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="N65" s="33" t="n">
-        <v>36.89</v>
+      <c r="M65" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="N65" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="O65" s="33" t="n">
-        <v>9.78</v>
+        <v>45</v>
       </c>
       <c r="P65" s="1"/>
       <c r="Q65" s="12"/>
@@ -5305,14 +5351,14 @@
       <c r="L66" s="31" t="n">
         <v>17.86</v>
       </c>
-      <c r="M66" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="N66" s="33" t="n">
-        <v>15.1</v>
+      <c r="M66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N66" s="33" t="s">
+        <v>85</v>
       </c>
       <c r="O66" s="33" t="n">
-        <v>7.09</v>
+        <v>32.6</v>
       </c>
       <c r="P66" s="1"/>
       <c r="Q66" s="12"/>
@@ -5368,14 +5414,14 @@
       <c r="L67" s="31" t="n">
         <v>17.26</v>
       </c>
-      <c r="M67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="33" t="n">
-        <v>0</v>
+      <c r="M67" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="N67" s="33" t="s">
+        <v>60</v>
       </c>
       <c r="O67" s="33" t="n">
-        <v>7.87</v>
+        <v>36.2</v>
       </c>
       <c r="P67" s="1"/>
       <c r="Q67" s="12"/>
@@ -5405,40 +5451,40 @@
         <v>10.22</v>
       </c>
       <c r="D68" s="31" t="n">
-        <v>2.76</v>
+        <v>3.44</v>
       </c>
       <c r="E68" s="33" t="n">
         <v>28.4</v>
       </c>
       <c r="F68" s="31" t="n">
-        <v>38.26</v>
+        <v>47.82</v>
       </c>
       <c r="G68" s="33" t="n">
         <v>9.73</v>
       </c>
       <c r="H68" s="31" t="n">
-        <v>9.25</v>
+        <v>11.56</v>
       </c>
       <c r="I68" s="33" t="n">
         <v>4.89</v>
       </c>
       <c r="J68" s="31" t="n">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="K68" s="33" t="n">
         <v>13.16</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="M68" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="33" t="n">
-        <v>0</v>
+        <v>16.7</v>
+      </c>
+      <c r="M68" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="N68" s="33" t="s">
+        <v>60</v>
       </c>
       <c r="O68" s="33" t="n">
-        <v>7.91</v>
+        <v>36.4</v>
       </c>
       <c r="P68" s="1"/>
       <c r="Q68" s="12"/>
@@ -5606,7 +5652,7 @@
     <row r="73">
       <c r="A73" s="1"/>
       <c r="B73" s="5" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C73" s="36" t="s">
         <v>4</v>
@@ -5997,15 +6043,9 @@
       <c r="B80" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
       <c r="F80" s="32" t="n">
         <v>0</v>
       </c>
@@ -6058,15 +6098,9 @@
       <c r="B81" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C81" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>0</v>
-      </c>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
       <c r="F81" s="31" t="n">
         <v>0</v>
       </c>
@@ -38831,58 +38865,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="I1" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="K1" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="L1" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="M1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="N1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="O1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="P1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="Q1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="R1" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
@@ -38890,7 +38924,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="n">
@@ -38900,25 +38934,25 @@
         <v>46273</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -38933,7 +38967,7 @@
         <v>7</v>
       </c>
       <c r="Q2" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -38944,7 +38978,7 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="n">
@@ -38954,25 +38988,25 @@
         <v>46273</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -38987,7 +39021,7 @@
         <v>50</v>
       </c>
       <c r="Q3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -38998,7 +39032,7 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="n">
@@ -39008,25 +39042,25 @@
         <v>46273</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L4" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -39041,7 +39075,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -39052,7 +39086,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="n">
@@ -39062,25 +39096,25 @@
         <v>46273</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -39095,7 +39129,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -39106,7 +39140,7 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="n">
@@ -39116,25 +39150,25 @@
         <v>46273</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -39149,7 +39183,7 @@
         <v>41</v>
       </c>
       <c r="Q6" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -39160,7 +39194,7 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="n">
@@ -39170,25 +39204,25 @@
         <v>46273</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -39203,7 +39237,7 @@
         <v>8</v>
       </c>
       <c r="Q7" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -39214,7 +39248,7 @@
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="n">
@@ -39224,25 +39258,25 @@
         <v>46273</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -39257,7 +39291,7 @@
         <v>42</v>
       </c>
       <c r="Q8" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -39268,7 +39302,7 @@
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="n">
@@ -39278,25 +39312,25 @@
         <v>46274</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
@@ -39309,7 +39343,7 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -39320,7 +39354,7 @@
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="n">
@@ -39330,25 +39364,25 @@
         <v>46274</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L10" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
@@ -39361,7 +39395,7 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -39372,7 +39406,7 @@
         <v>2026</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="n">
@@ -39382,25 +39416,25 @@
         <v>46274</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -39413,7 +39447,7 @@
         <v>6</v>
       </c>
       <c r="Q11" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -39424,7 +39458,7 @@
         <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="n">
@@ -39434,25 +39468,25 @@
         <v>46274</v>
       </c>
       <c r="F12" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
@@ -39465,7 +39499,7 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -39476,7 +39510,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="n">
@@ -39486,25 +39520,25 @@
         <v>46274</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
@@ -39517,7 +39551,7 @@
         <v>5</v>
       </c>
       <c r="Q13" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -39528,7 +39562,7 @@
         <v>2026</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="n">
@@ -39538,25 +39572,25 @@
         <v>46274</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
@@ -39569,7 +39603,7 @@
         <v>15</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -39580,7 +39614,7 @@
         <v>2026</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="n">
@@ -39590,25 +39624,25 @@
         <v>46274</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
@@ -39621,7 +39655,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -39632,7 +39666,7 @@
         <v>2026</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="n">
@@ -39642,25 +39676,25 @@
         <v>46274</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
@@ -39673,7 +39707,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -39684,7 +39718,7 @@
         <v>2026</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="n">
@@ -39694,25 +39728,25 @@
         <v>46274</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J17" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" t="s">
         <v>109</v>
       </c>
-      <c r="K17" t="s">
-        <v>79</v>
-      </c>
       <c r="L17" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -39725,7 +39759,7 @@
         <v>50</v>
       </c>
       <c r="Q17" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -39736,7 +39770,7 @@
         <v>2026</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="n">
@@ -39746,25 +39780,25 @@
         <v>46274</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" t="s">
         <v>109</v>
       </c>
-      <c r="K18" t="s">
-        <v>79</v>
-      </c>
       <c r="L18" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
@@ -39777,7 +39811,7 @@
         <v>13</v>
       </c>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -39788,7 +39822,7 @@
         <v>2026</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="n">
@@ -39798,25 +39832,25 @@
         <v>46274</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="I19" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
@@ -39829,7 +39863,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -39840,7 +39874,7 @@
         <v>2026</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="n">
@@ -39850,25 +39884,25 @@
         <v>46274</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" t="s">
         <v>113</v>
-      </c>
-      <c r="I20" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20" t="s">
-        <v>78</v>
-      </c>
-      <c r="K20" t="s">
-        <v>79</v>
-      </c>
-      <c r="L20" t="s">
-        <v>83</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
@@ -39881,7 +39915,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -39892,7 +39926,7 @@
         <v>2026</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="n">
@@ -39902,25 +39936,25 @@
         <v>46274</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="I21" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
@@ -39933,7 +39967,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -39944,7 +39978,7 @@
         <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="n">
@@ -39954,25 +39988,25 @@
         <v>46274</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J22" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" t="s">
         <v>109</v>
       </c>
-      <c r="K22" t="s">
-        <v>79</v>
-      </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
@@ -39985,7 +40019,7 @@
         <v>50</v>
       </c>
       <c r="Q22" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -39996,7 +40030,7 @@
         <v>2026</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="n">
@@ -40006,25 +40040,25 @@
         <v>46274</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="I23" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J23" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" t="s">
         <v>109</v>
       </c>
-      <c r="K23" t="s">
-        <v>79</v>
-      </c>
       <c r="L23" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
@@ -40037,7 +40071,7 @@
         <v>50</v>
       </c>
       <c r="Q23" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -40048,7 +40082,7 @@
         <v>2026</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="n">
@@ -40058,25 +40092,25 @@
         <v>46274</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J24" t="s">
+        <v>139</v>
+      </c>
+      <c r="K24" t="s">
         <v>109</v>
       </c>
-      <c r="K24" t="s">
-        <v>79</v>
-      </c>
       <c r="L24" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
@@ -40089,7 +40123,7 @@
         <v>50</v>
       </c>
       <c r="Q24" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -40100,7 +40134,7 @@
         <v>2026</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="n">
@@ -40110,25 +40144,25 @@
         <v>46274</v>
       </c>
       <c r="F25" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K25" t="s">
         <v>109</v>
       </c>
-      <c r="K25" t="s">
-        <v>79</v>
-      </c>
       <c r="L25" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -40141,7 +40175,7 @@
         <v>23</v>
       </c>
       <c r="Q25" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -40152,7 +40186,7 @@
         <v>2026</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="n">
@@ -40162,25 +40196,25 @@
         <v>46274</v>
       </c>
       <c r="F26" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="I26" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K26" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
@@ -40193,7 +40227,7 @@
         <v>5</v>
       </c>
       <c r="Q26" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -40204,7 +40238,7 @@
         <v>2026</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="n">
@@ -40214,25 +40248,25 @@
         <v>46274</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="I27" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J27" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" t="s">
         <v>109</v>
       </c>
-      <c r="K27" t="s">
-        <v>79</v>
-      </c>
       <c r="L27" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
@@ -40245,7 +40279,7 @@
         <v>18</v>
       </c>
       <c r="Q27" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -40256,7 +40290,7 @@
         <v>2026</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="n">
@@ -40266,25 +40300,25 @@
         <v>46274</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="I28" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K28" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -40297,7 +40331,7 @@
         <v>3</v>
       </c>
       <c r="Q28" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -40308,7 +40342,7 @@
         <v>2026</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="n">
@@ -40318,25 +40352,25 @@
         <v>46274</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="I29" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K29" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -40349,7 +40383,7 @@
         <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -40360,7 +40394,7 @@
         <v>2026</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="n">
@@ -40370,25 +40404,25 @@
         <v>46274</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="I30" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J30" t="s">
+        <v>139</v>
+      </c>
+      <c r="K30" t="s">
         <v>109</v>
       </c>
-      <c r="K30" t="s">
-        <v>79</v>
-      </c>
       <c r="L30" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -40401,7 +40435,7 @@
         <v>50</v>
       </c>
       <c r="Q30" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -40412,7 +40446,7 @@
         <v>2026</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="n">
@@ -40422,25 +40456,25 @@
         <v>46274</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="I31" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K31" t="s">
         <v>109</v>
       </c>
-      <c r="K31" t="s">
-        <v>79</v>
-      </c>
       <c r="L31" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -40453,7 +40487,7 @@
         <v>15</v>
       </c>
       <c r="Q31" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -40464,7 +40498,7 @@
         <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="n">
@@ -40474,25 +40508,25 @@
         <v>46274</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="I32" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J32" t="s">
+        <v>139</v>
+      </c>
+      <c r="K32" t="s">
         <v>109</v>
       </c>
-      <c r="K32" t="s">
-        <v>79</v>
-      </c>
       <c r="L32" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -40505,7 +40539,7 @@
         <v>19</v>
       </c>
       <c r="Q32" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -40516,7 +40550,7 @@
         <v>2026</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="n">
@@ -40526,25 +40560,25 @@
         <v>46274</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="I33" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K33" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L33" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -40557,7 +40591,7 @@
         <v>5</v>
       </c>
       <c r="Q33" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -40568,7 +40602,7 @@
         <v>2026</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="n">
@@ -40578,25 +40612,25 @@
         <v>46274</v>
       </c>
       <c r="F34" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="I34" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K34" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -40609,7 +40643,7 @@
         <v>32</v>
       </c>
       <c r="Q34" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -40620,7 +40654,7 @@
         <v>2026</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="n">
@@ -40630,25 +40664,25 @@
         <v>46274</v>
       </c>
       <c r="F35" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="I35" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J35" t="s">
+        <v>139</v>
+      </c>
+      <c r="K35" t="s">
         <v>109</v>
       </c>
-      <c r="K35" t="s">
-        <v>79</v>
-      </c>
       <c r="L35" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -40661,7 +40695,7 @@
         <v>9</v>
       </c>
       <c r="Q35" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -40672,7 +40706,7 @@
         <v>2026</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="n">
@@ -40682,25 +40716,25 @@
         <v>46274</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K36" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L36" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -40713,7 +40747,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -40724,7 +40758,7 @@
         <v>2026</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="n">
@@ -40734,25 +40768,25 @@
         <v>46274</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
@@ -40765,7 +40799,7 @@
         <v>4</v>
       </c>
       <c r="Q37" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -40776,7 +40810,7 @@
         <v>2026</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="n">
@@ -40786,25 +40820,25 @@
         <v>46274</v>
       </c>
       <c r="F38" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="I38" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J38" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K38" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -40817,7 +40851,7 @@
         <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -40828,7 +40862,7 @@
         <v>2026</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="n">
@@ -40838,25 +40872,25 @@
         <v>46274</v>
       </c>
       <c r="F39" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="I39" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J39" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -40869,7 +40903,7 @@
         <v>2</v>
       </c>
       <c r="Q39" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -40880,7 +40914,7 @@
         <v>2026</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="C40"/>
       <c r="D40" t="n">
@@ -40890,25 +40924,25 @@
         <v>46274</v>
       </c>
       <c r="F40" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G40" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="I40" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J40" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K40" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -40921,7 +40955,7 @@
         <v>6</v>
       </c>
       <c r="Q40" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -40932,7 +40966,7 @@
         <v>2026</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="C41"/>
       <c r="D41" t="n">
@@ -40942,25 +40976,25 @@
         <v>46274</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="I41" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J41" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K41" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -40973,7 +41007,7 @@
         <v>49</v>
       </c>
       <c r="Q41" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -40984,7 +41018,7 @@
         <v>2026</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C42"/>
       <c r="D42" t="n">
@@ -40994,25 +41028,25 @@
         <v>46274</v>
       </c>
       <c r="F42" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="I42" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J42" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -41025,7 +41059,7 @@
         <v>5</v>
       </c>
       <c r="Q42" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -41036,7 +41070,7 @@
         <v>2026</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="C43"/>
       <c r="D43" t="n">
@@ -41046,25 +41080,25 @@
         <v>46274</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G43" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="I43" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J43" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K43" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -41077,7 +41111,7 @@
         <v>50</v>
       </c>
       <c r="Q43" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -41088,7 +41122,7 @@
         <v>2026</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="C44"/>
       <c r="D44" t="n">
@@ -41098,25 +41132,25 @@
         <v>46274</v>
       </c>
       <c r="F44" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G44" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="I44" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J44" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K44" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -41129,7 +41163,7 @@
         <v>41</v>
       </c>
       <c r="Q44" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -41140,7 +41174,7 @@
         <v>2026</v>
       </c>
       <c r="B45" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="C45"/>
       <c r="D45" t="n">
@@ -41150,25 +41184,25 @@
         <v>46274</v>
       </c>
       <c r="F45" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H45" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I45" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J45" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K45" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -41181,7 +41215,7 @@
         <v>2</v>
       </c>
       <c r="Q45" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -41192,7 +41226,7 @@
         <v>2026</v>
       </c>
       <c r="B46" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="C46"/>
       <c r="D46" t="n">
@@ -41202,25 +41236,25 @@
         <v>46274</v>
       </c>
       <c r="F46" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I46" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J46" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L46" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -41233,7 +41267,7 @@
         <v>16</v>
       </c>
       <c r="Q46" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -41244,7 +41278,7 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C47"/>
       <c r="D47" t="n">
@@ -41254,25 +41288,25 @@
         <v>46274</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G47" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="I47" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J47" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K47" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -41285,7 +41319,7 @@
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -41296,7 +41330,7 @@
         <v>2026</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="C48"/>
       <c r="D48" t="n">
@@ -41306,25 +41340,25 @@
         <v>46274</v>
       </c>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G48" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="I48" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J48" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K48" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -41337,7 +41371,7 @@
         <v>2</v>
       </c>
       <c r="Q48" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -41348,7 +41382,7 @@
         <v>2026</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="C49"/>
       <c r="D49" t="n">
@@ -41358,25 +41392,25 @@
         <v>46274</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G49" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="I49" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J49" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K49" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L49" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -41389,7 +41423,7 @@
         <v>8</v>
       </c>
       <c r="Q49" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -41400,7 +41434,7 @@
         <v>2026</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C50"/>
       <c r="D50" t="n">
@@ -41410,25 +41444,25 @@
         <v>46274</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G50" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H50" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I50" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J50" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K50" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L50" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -41441,7 +41475,7 @@
         <v>11</v>
       </c>
       <c r="Q50" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -41452,7 +41486,7 @@
         <v>2026</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C51"/>
       <c r="D51" t="n">
@@ -41462,25 +41496,25 @@
         <v>46274</v>
       </c>
       <c r="F51" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H51" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I51" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J51" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -41493,7 +41527,7 @@
         <v>24</v>
       </c>
       <c r="Q51" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -41504,7 +41538,7 @@
         <v>2026</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="C52"/>
       <c r="D52" t="n">
@@ -41514,25 +41548,25 @@
         <v>46274</v>
       </c>
       <c r="F52" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G52" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H52" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="I52" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J52" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K52" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L52" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -41545,7 +41579,7 @@
         <v>5</v>
       </c>
       <c r="Q52" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -41556,7 +41590,7 @@
         <v>2026</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C53"/>
       <c r="D53" t="n">
@@ -41566,25 +41600,25 @@
         <v>46274</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G53" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H53" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="I53" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="J53" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K53" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -41597,7 +41631,7 @@
         <v>23</v>
       </c>
       <c r="Q53" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -41608,7 +41642,7 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="n">
@@ -41618,25 +41652,25 @@
         <v>46274</v>
       </c>
       <c r="F54" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G54" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H54" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="I54" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J54" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K54" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L54" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -41649,7 +41683,7 @@
         <v>6</v>
       </c>
       <c r="Q54" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -41660,7 +41694,7 @@
         <v>2026</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="C55"/>
       <c r="D55" t="n">
@@ -41670,25 +41704,25 @@
         <v>46274</v>
       </c>
       <c r="F55" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G55" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H55" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="I55" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J55" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K55" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -41701,7 +41735,7 @@
         <v>7</v>
       </c>
       <c r="Q55" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -41712,7 +41746,7 @@
         <v>2026</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C56"/>
       <c r="D56" t="n">
@@ -41722,25 +41756,25 @@
         <v>46275</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H56" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="I56" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J56" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K56" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -41753,7 +41787,7 @@
         <v>9</v>
       </c>
       <c r="Q56" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -41764,7 +41798,7 @@
         <v>2026</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="C57"/>
       <c r="D57" t="n">
@@ -41774,25 +41808,25 @@
         <v>46275</v>
       </c>
       <c r="F57" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G57" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H57" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="I57" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J57" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K57" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L57" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -41805,7 +41839,7 @@
         <v>3</v>
       </c>
       <c r="Q57" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -41816,7 +41850,7 @@
         <v>2026</v>
       </c>
       <c r="B58" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="C58"/>
       <c r="D58" t="n">
@@ -41826,25 +41860,25 @@
         <v>46275</v>
       </c>
       <c r="F58" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G58" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H58" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="I58" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J58" t="s">
+        <v>139</v>
+      </c>
+      <c r="K58" t="s">
         <v>109</v>
       </c>
-      <c r="K58" t="s">
-        <v>79</v>
-      </c>
       <c r="L58" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -41857,7 +41891,7 @@
         <v>50</v>
       </c>
       <c r="Q58" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -41868,7 +41902,7 @@
         <v>2026</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="C59"/>
       <c r="D59" t="n">
@@ -41878,25 +41912,25 @@
         <v>46275</v>
       </c>
       <c r="F59" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G59" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H59" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="I59" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J59" t="s">
+        <v>139</v>
+      </c>
+      <c r="K59" t="s">
         <v>109</v>
       </c>
-      <c r="K59" t="s">
-        <v>79</v>
-      </c>
       <c r="L59" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -41909,7 +41943,7 @@
         <v>36</v>
       </c>
       <c r="Q59" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
@@ -41920,7 +41954,7 @@
         <v>2026</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="C60"/>
       <c r="D60" t="n">
@@ -41930,25 +41964,25 @@
         <v>46275</v>
       </c>
       <c r="F60" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G60" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H60" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I60" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J60" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K60" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -41961,7 +41995,7 @@
         <v>3</v>
       </c>
       <c r="Q60" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -41972,7 +42006,7 @@
         <v>2026</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C61"/>
       <c r="D61" t="n">
@@ -41982,25 +42016,25 @@
         <v>46275</v>
       </c>
       <c r="F61" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G61" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H61" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="I61" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J61" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K61" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L61" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -42013,7 +42047,7 @@
         <v>4</v>
       </c>
       <c r="Q61" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -42024,7 +42058,7 @@
         <v>2026</v>
       </c>
       <c r="B62" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="C62"/>
       <c r="D62" t="n">
@@ -42034,25 +42068,25 @@
         <v>46275</v>
       </c>
       <c r="F62" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G62" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H62" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="I62" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J62" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K62" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L62" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -42065,7 +42099,7 @@
         <v>3</v>
       </c>
       <c r="Q62" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -42076,7 +42110,7 @@
         <v>2026</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C63"/>
       <c r="D63" t="n">
@@ -42086,25 +42120,25 @@
         <v>46275</v>
       </c>
       <c r="F63" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G63" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H63" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="I63" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J63" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K63" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L63" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -42117,7 +42151,7 @@
         <v>2</v>
       </c>
       <c r="Q63" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -42128,7 +42162,7 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C64"/>
       <c r="D64" t="n">
@@ -42138,25 +42172,25 @@
         <v>46275</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G64" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H64" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="I64" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J64" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K64" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -42169,7 +42203,7 @@
         <v>6</v>
       </c>
       <c r="Q64" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -42180,7 +42214,7 @@
         <v>2026</v>
       </c>
       <c r="B65" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="C65"/>
       <c r="D65" t="n">
@@ -42190,25 +42224,25 @@
         <v>46275</v>
       </c>
       <c r="F65" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G65" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H65" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="I65" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J65" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K65" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L65" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -42221,7 +42255,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -42232,7 +42266,7 @@
         <v>2026</v>
       </c>
       <c r="B66" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C66"/>
       <c r="D66" t="n">
@@ -42242,25 +42276,25 @@
         <v>46275</v>
       </c>
       <c r="F66" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G66" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H66" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="I66" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J66" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K66" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -42273,7 +42307,7 @@
         <v>10</v>
       </c>
       <c r="Q66" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -42284,7 +42318,7 @@
         <v>2026</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C67"/>
       <c r="D67" t="n">
@@ -42294,25 +42328,25 @@
         <v>46275</v>
       </c>
       <c r="F67" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G67" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H67" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J67" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K67" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -42325,7 +42359,7 @@
         <v>3</v>
       </c>
       <c r="Q67" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -42336,7 +42370,7 @@
         <v>2026</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="C68"/>
       <c r="D68" t="n">
@@ -42346,25 +42380,25 @@
         <v>46275</v>
       </c>
       <c r="F68" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G68" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H68" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="I68" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J68" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K68" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -42377,7 +42411,7 @@
         <v>7</v>
       </c>
       <c r="Q68" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -42388,7 +42422,7 @@
         <v>2026</v>
       </c>
       <c r="B69" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C69"/>
       <c r="D69" t="n">
@@ -42398,25 +42432,25 @@
         <v>46275</v>
       </c>
       <c r="F69" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G69" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H69" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="I69" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J69" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K69" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -42429,7 +42463,7 @@
         <v>11</v>
       </c>
       <c r="Q69" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -42440,7 +42474,7 @@
         <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C70"/>
       <c r="D70" t="n">
@@ -42450,25 +42484,25 @@
         <v>46275</v>
       </c>
       <c r="F70" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G70" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H70" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="I70" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J70" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K70" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L70" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -42481,7 +42515,7 @@
         <v>2</v>
       </c>
       <c r="Q70" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -42492,7 +42526,7 @@
         <v>2026</v>
       </c>
       <c r="B71" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="C71"/>
       <c r="D71" t="n">
@@ -42502,25 +42536,25 @@
         <v>46275</v>
       </c>
       <c r="F71" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G71" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H71" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="I71" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J71" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K71" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L71" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -42533,7 +42567,7 @@
         <v>6</v>
       </c>
       <c r="Q71" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -42544,7 +42578,7 @@
         <v>2026</v>
       </c>
       <c r="B72" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C72"/>
       <c r="D72" t="n">
@@ -42554,25 +42588,25 @@
         <v>46275</v>
       </c>
       <c r="F72" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G72" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H72" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I72" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J72" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K72" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L72" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -42585,7 +42619,7 @@
         <v>2</v>
       </c>
       <c r="Q72" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -42596,7 +42630,7 @@
         <v>2026</v>
       </c>
       <c r="B73" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="C73"/>
       <c r="D73" t="n">
@@ -42606,25 +42640,25 @@
         <v>46275</v>
       </c>
       <c r="F73" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G73" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H73" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I73" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J73" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K73" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L73" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -42637,7 +42671,7 @@
         <v>22</v>
       </c>
       <c r="Q73" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -42648,7 +42682,7 @@
         <v>2026</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="C74"/>
       <c r="D74" t="n">
@@ -42658,25 +42692,25 @@
         <v>46275</v>
       </c>
       <c r="F74" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G74" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H74" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="I74" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J74" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K74" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -42689,7 +42723,7 @@
         <v>1</v>
       </c>
       <c r="Q74" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -42700,7 +42734,7 @@
         <v>2026</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="C75"/>
       <c r="D75" t="n">
@@ -42710,25 +42744,25 @@
         <v>46275</v>
       </c>
       <c r="F75" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G75" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H75" t="s">
+        <v>235</v>
+      </c>
+      <c r="I75" t="s">
         <v>205</v>
       </c>
-      <c r="I75" t="s">
-        <v>175</v>
-      </c>
       <c r="J75" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K75" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -42741,7 +42775,7 @@
         <v>1</v>
       </c>
       <c r="Q75" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -42752,7 +42786,7 @@
         <v>2026</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="C76"/>
       <c r="D76" t="n">
@@ -42762,25 +42796,25 @@
         <v>46275</v>
       </c>
       <c r="F76" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G76" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H76" t="s">
+        <v>235</v>
+      </c>
+      <c r="I76" t="s">
         <v>205</v>
       </c>
-      <c r="I76" t="s">
-        <v>175</v>
-      </c>
       <c r="J76" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K76" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L76" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -42793,7 +42827,7 @@
         <v>4</v>
       </c>
       <c r="Q76" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -42804,7 +42838,7 @@
         <v>2026</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C77"/>
       <c r="D77" t="n">
@@ -42814,25 +42848,25 @@
         <v>46275</v>
       </c>
       <c r="F77" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G77" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H77" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="I77" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J77" t="s">
+        <v>139</v>
+      </c>
+      <c r="K77" t="s">
         <v>109</v>
       </c>
-      <c r="K77" t="s">
-        <v>79</v>
-      </c>
       <c r="L77" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -42845,7 +42879,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -42856,7 +42890,7 @@
         <v>2026</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C78"/>
       <c r="D78" t="n">
@@ -42866,25 +42900,25 @@
         <v>46275</v>
       </c>
       <c r="F78" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G78" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H78" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="I78" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J78" t="s">
+        <v>139</v>
+      </c>
+      <c r="K78" t="s">
         <v>109</v>
       </c>
-      <c r="K78" t="s">
-        <v>79</v>
-      </c>
       <c r="L78" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -42897,7 +42931,7 @@
         <v>50</v>
       </c>
       <c r="Q78" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -42908,7 +42942,7 @@
         <v>2026</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="C79"/>
       <c r="D79" t="n">
@@ -42918,25 +42952,25 @@
         <v>46275</v>
       </c>
       <c r="F79" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G79" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H79" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="I79" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="J79" t="s">
+        <v>139</v>
+      </c>
+      <c r="K79" t="s">
         <v>109</v>
       </c>
-      <c r="K79" t="s">
-        <v>79</v>
-      </c>
       <c r="L79" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -42949,7 +42983,7 @@
         <v>21</v>
       </c>
       <c r="Q79" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -42960,7 +42994,7 @@
         <v>2026</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="C80"/>
       <c r="D80" t="n">
@@ -42970,25 +43004,25 @@
         <v>46275</v>
       </c>
       <c r="F80" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G80" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H80" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="I80" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J80" t="s">
+        <v>139</v>
+      </c>
+      <c r="K80" t="s">
         <v>109</v>
       </c>
-      <c r="K80" t="s">
-        <v>79</v>
-      </c>
       <c r="L80" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -43001,7 +43035,7 @@
         <v>27</v>
       </c>
       <c r="Q80" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -43012,7 +43046,7 @@
         <v>2026</v>
       </c>
       <c r="B81" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="C81"/>
       <c r="D81" t="n">
@@ -43022,25 +43056,25 @@
         <v>46275</v>
       </c>
       <c r="F81" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G81" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H81" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="I81" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J81" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K81" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L81" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -43053,7 +43087,7 @@
         <v>4</v>
       </c>
       <c r="Q81" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -43064,7 +43098,7 @@
         <v>2026</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C82"/>
       <c r="D82" t="n">
@@ -43074,25 +43108,25 @@
         <v>46275</v>
       </c>
       <c r="F82" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G82" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H82" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="I82" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J82" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K82" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L82" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -43105,7 +43139,7 @@
         <v>15</v>
       </c>
       <c r="Q82" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -43116,7 +43150,7 @@
         <v>2026</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="C83"/>
       <c r="D83" t="n">
@@ -43126,25 +43160,25 @@
         <v>46275</v>
       </c>
       <c r="F83" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G83" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H83" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="I83" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J83" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K83" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L83" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -43157,7 +43191,7 @@
         <v>4</v>
       </c>
       <c r="Q83" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -43168,7 +43202,7 @@
         <v>2026</v>
       </c>
       <c r="B84" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="C84"/>
       <c r="D84" t="n">
@@ -43178,25 +43212,25 @@
         <v>46275</v>
       </c>
       <c r="F84" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G84" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H84" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="I84" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J84" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K84" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L84" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -43209,7 +43243,7 @@
         <v>4</v>
       </c>
       <c r="Q84" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -43220,7 +43254,7 @@
         <v>2026</v>
       </c>
       <c r="B85" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C85"/>
       <c r="D85" t="n">
@@ -43230,25 +43264,25 @@
         <v>46275</v>
       </c>
       <c r="F85" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G85" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H85" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="I85" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J85" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K85" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -43261,7 +43295,7 @@
         <v>2</v>
       </c>
       <c r="Q85" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -43272,7 +43306,7 @@
         <v>2026</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="C86"/>
       <c r="D86" t="n">
@@ -43282,25 +43316,25 @@
         <v>46275</v>
       </c>
       <c r="F86" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G86" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H86" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="I86" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J86" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K86" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L86" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -43313,7 +43347,7 @@
         <v>1</v>
       </c>
       <c r="Q86" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -43324,7 +43358,7 @@
         <v>2026</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="C87"/>
       <c r="D87" t="n">
@@ -43334,25 +43368,25 @@
         <v>46275</v>
       </c>
       <c r="F87" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G87" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H87" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="I87" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J87" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K87" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L87" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -43365,7 +43399,7 @@
         <v>1</v>
       </c>
       <c r="Q87" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -43376,7 +43410,7 @@
         <v>2026</v>
       </c>
       <c r="B88" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C88"/>
       <c r="D88" t="n">
@@ -43386,25 +43420,25 @@
         <v>46275</v>
       </c>
       <c r="F88" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G88" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H88" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="I88" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J88" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K88" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L88" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -43417,7 +43451,7 @@
         <v>10</v>
       </c>
       <c r="Q88" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -43428,7 +43462,7 @@
         <v>2026</v>
       </c>
       <c r="B89" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="C89"/>
       <c r="D89" t="n">
@@ -43438,25 +43472,25 @@
         <v>46275</v>
       </c>
       <c r="F89" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G89" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H89" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="I89" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J89" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K89" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L89" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -43469,7 +43503,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -43480,7 +43514,7 @@
         <v>2026</v>
       </c>
       <c r="B90" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="C90"/>
       <c r="D90" t="n">
@@ -43490,25 +43524,25 @@
         <v>46275</v>
       </c>
       <c r="F90" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G90" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H90" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="I90" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J90" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K90" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L90" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -43521,7 +43555,7 @@
         <v>9</v>
       </c>
       <c r="Q90" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -43532,7 +43566,7 @@
         <v>2026</v>
       </c>
       <c r="B91" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C91"/>
       <c r="D91" t="n">
@@ -43542,25 +43576,25 @@
         <v>46275</v>
       </c>
       <c r="F91" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G91" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H91" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="I91" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J91" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K91" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L91" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -43573,7 +43607,7 @@
         <v>4</v>
       </c>
       <c r="Q91" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -43584,7 +43618,7 @@
         <v>2026</v>
       </c>
       <c r="B92" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="C92"/>
       <c r="D92" t="n">
@@ -43594,25 +43628,25 @@
         <v>46275</v>
       </c>
       <c r="F92" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G92" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H92" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="I92" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J92" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K92" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -43625,7 +43659,7 @@
         <v>2</v>
       </c>
       <c r="Q92" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -43644,33 +43678,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="C1" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D1" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="E1" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="F1" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="G1" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="H1" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B2" t="n">
         <v>8.1111</v>
@@ -43696,7 +43730,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B3" t="n">
         <v>23.4</v>
@@ -43722,7 +43756,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="B4" t="n">
         <v>7.6667</v>
@@ -43748,7 +43782,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="B5" t="n">
         <v>4.3333</v>
@@ -43774,7 +43808,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B6" t="n">
         <v>10.7209</v>
@@ -43810,65 +43844,45 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B10" t="n">
-        <v>7.087</v>
+        <v>32.6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8261</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -43899,46 +43913,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B1" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C1" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D1" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="F1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="H1" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="K1" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="L1" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="M1" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="N1" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -43975,11 +43989,11 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" t="s">
+        <v>56</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -44019,11 +44033,11 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" t="s">
+        <v>56</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -44063,11 +44077,11 @@
       <c r="K4" t="n">
         <v>0.01</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" t="s">
+        <v>56</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -44107,11 +44121,11 @@
       <c r="K5" t="n">
         <v>0.02</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -44151,11 +44165,11 @@
       <c r="K6" t="n">
         <v>0.04</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -44195,14 +44209,14 @@
       <c r="K7" t="n">
         <v>0.17</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="8">
@@ -44239,11 +44253,11 @@
       <c r="K8" t="n">
         <v>0.36</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -44283,11 +44297,11 @@
       <c r="K9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -44327,11 +44341,11 @@
       <c r="K10" t="n">
         <v>0.32</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -44371,11 +44385,11 @@
       <c r="K11" t="n">
         <v>0.31</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>56</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -44415,11 +44429,11 @@
       <c r="K12" t="n">
         <v>0.3</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.35</v>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" t="s">
+        <v>59</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -44459,11 +44473,11 @@
       <c r="K13" t="n">
         <v>0.33</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" t="s">
+        <v>56</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -44503,11 +44517,11 @@
       <c r="K14" t="n">
         <v>0.17</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" t="s">
+        <v>56</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -44547,11 +44561,11 @@
       <c r="K15" t="n">
         <v>0.11</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -44565,13 +44579,13 @@
         <v>0.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D16" t="n">
         <v>0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
         <v>0.04</v>
@@ -44589,13 +44603,13 @@
         <v>0.08</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+        <v>0.07</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" t="s">
+        <v>60</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -44614,33 +44628,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="G1" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="H1" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B2" t="n">
         <v>73</v>
@@ -44666,7 +44680,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B3" t="n">
         <v>234</v>
@@ -44692,7 +44706,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="B4" t="n">
         <v>115</v>
@@ -44718,7 +44732,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="B5" t="n">
         <v>39</v>
@@ -44744,7 +44758,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B6" t="n">
         <v>461</v>
@@ -44780,59 +44794,35 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
       <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
       <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B10" t="n">
         <v>163</v>
@@ -44844,16 +44834,16 @@
         <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>7.09</v>
+        <v>32.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.83</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>7.91</v>
+        <v>36.4</v>
       </c>
     </row>
   </sheetData>
@@ -44869,46 +44859,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B1" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C1" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="E1" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="F1" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="J1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="K1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="L1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="M1" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="N1" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2">
@@ -44919,40 +44909,40 @@
         <v>1.22</v>
       </c>
       <c r="C2" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="D2" t="n">
         <v>2.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.22</v>
+        <v>4.03</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85</v>
+        <v>3.56</v>
       </c>
       <c r="H2" t="n">
         <v>0.89</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>3.22</v>
       </c>
       <c r="J2" t="n">
         <v>1.33</v>
       </c>
       <c r="K2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.4</v>
+        <v>3.46</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>62</v>
       </c>
       <c r="N2" t="n">
-        <v>5.04</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="3">
@@ -44963,40 +44953,40 @@
         <v>1.44</v>
       </c>
       <c r="C3" t="n">
-        <v>3.22</v>
+        <v>4.03</v>
       </c>
       <c r="D3" t="n">
         <v>4.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.14</v>
+        <v>5.18</v>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.07</v>
+        <v>6.33</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.89</v>
+        <v>3.61</v>
       </c>
       <c r="J3" t="n">
         <v>2.47</v>
       </c>
       <c r="K3" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="L3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.8</v>
+        <v>5.01</v>
+      </c>
+      <c r="L3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" t="s">
+        <v>64</v>
       </c>
       <c r="N3" t="n">
-        <v>4.48</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="4">
@@ -45033,14 +45023,14 @@
       <c r="K4" t="n">
         <v>14.24</v>
       </c>
-      <c r="L4" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5.4</v>
+      <c r="L4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" t="s">
+        <v>66</v>
       </c>
       <c r="N4" t="n">
-        <v>6.39</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="5">
@@ -45077,14 +45067,14 @@
       <c r="K5" t="n">
         <v>46.27</v>
       </c>
-      <c r="L5" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M5" t="n">
-        <v>23.7</v>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" t="s">
+        <v>68</v>
       </c>
       <c r="N5" t="n">
-        <v>23.65</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="6">
@@ -45121,14 +45111,14 @@
       <c r="K6" t="n">
         <v>73.21</v>
       </c>
-      <c r="L6" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="M6" t="n">
-        <v>13.9</v>
+      <c r="L6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>21.87</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="7">
@@ -45165,14 +45155,14 @@
       <c r="K7" t="n">
         <v>115.14</v>
       </c>
-      <c r="L7" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="M7" t="n">
-        <v>27.4</v>
+      <c r="L7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" t="s">
+        <v>72</v>
       </c>
       <c r="N7" t="n">
-        <v>23.57</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="8">
@@ -45209,14 +45199,14 @@
       <c r="K8" t="n">
         <v>135.15</v>
       </c>
-      <c r="L8" t="n">
-        <v>21</v>
-      </c>
-      <c r="M8" t="n">
-        <v>27.4</v>
+      <c r="L8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" t="s">
+        <v>72</v>
       </c>
       <c r="N8" t="n">
-        <v>24.13</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
@@ -45253,14 +45243,14 @@
       <c r="K9" t="n">
         <v>79.9</v>
       </c>
-      <c r="L9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10.6</v>
+      <c r="L9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" t="s">
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>24.83</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="10">
@@ -45297,14 +45287,14 @@
       <c r="K10" t="n">
         <v>54.45</v>
       </c>
-      <c r="L10" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12.6</v>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>77</v>
       </c>
       <c r="N10" t="n">
-        <v>19.17</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="11">
@@ -45341,14 +45331,14 @@
       <c r="K11" t="n">
         <v>47.21</v>
       </c>
-      <c r="L11" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="M11" t="n">
-        <v>28.4</v>
+      <c r="L11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" t="s">
+        <v>79</v>
       </c>
       <c r="N11" t="n">
-        <v>16.7</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="12">
@@ -45385,14 +45375,14 @@
       <c r="K12" t="n">
         <v>34.73</v>
       </c>
-      <c r="L12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M12" t="n">
-        <v>124.44</v>
+      <c r="L12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" t="s">
+        <v>81</v>
       </c>
       <c r="N12" t="n">
-        <v>9.83</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="13">
@@ -45429,14 +45419,14 @@
       <c r="K13" t="n">
         <v>37.56</v>
       </c>
-      <c r="L13" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="M13" t="n">
-        <v>36.89</v>
+      <c r="L13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M13" t="s">
+        <v>83</v>
       </c>
       <c r="N13" t="n">
-        <v>9.78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -45473,14 +45463,14 @@
       <c r="K14" t="n">
         <v>17.86</v>
       </c>
-      <c r="L14" t="n">
-        <v>32</v>
-      </c>
-      <c r="M14" t="n">
-        <v>15.1</v>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" t="s">
+        <v>85</v>
       </c>
       <c r="N14" t="n">
-        <v>7.09</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="15">
@@ -45517,14 +45507,14 @@
       <c r="K15" t="n">
         <v>17.26</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>7.87</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="16">
@@ -45535,40 +45525,40 @@
         <v>10.22</v>
       </c>
       <c r="C16" t="n">
-        <v>2.76</v>
+        <v>3.44</v>
       </c>
       <c r="D16" t="n">
         <v>28.4</v>
       </c>
       <c r="E16" t="n">
-        <v>38.26</v>
+        <v>47.82</v>
       </c>
       <c r="F16" t="n">
         <v>9.73</v>
       </c>
       <c r="G16" t="n">
-        <v>9.25</v>
+        <v>11.56</v>
       </c>
       <c r="H16" t="n">
         <v>4.89</v>
       </c>
       <c r="I16" t="n">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
         <v>13.16</v>
       </c>
       <c r="K16" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+        <v>16.7</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" t="s">
+        <v>60</v>
       </c>
       <c r="N16" t="n">
-        <v>7.91</v>
+        <v>36.4</v>
       </c>
     </row>
   </sheetData>
@@ -45584,48 +45574,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="C1" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="E1" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="F1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="G1" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="H1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="I1" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="J1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="K1" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="L1" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="M1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B2" t="n">
         <v>73</v>
@@ -45666,7 +45656,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B3" t="n">
         <v>234</v>
@@ -45707,7 +45697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="B4" t="n">
         <v>115</v>
@@ -45748,7 +45738,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="B5" t="n">
         <v>39</v>
@@ -45789,7 +45779,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B6" t="n">
         <v>461</v>
@@ -45833,17 +45823,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
       <c r="E8" t="n">
         <v>0</v>
       </c>
@@ -45874,17 +45858,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -45915,7 +45893,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B10" t="n">
         <v>163</v>
@@ -45967,46 +45945,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="C1" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="D1" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="E1" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="F1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="G1" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="H1" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="J1" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="K1" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="L1" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="M1" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="N1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2">
